--- a/input/mapping/027. OCB_GOLD_TCKH_V_SBV_BAOANH.xlsx
+++ b/input/mapping/027. OCB_GOLD_TCKH_V_SBV_BAOANH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/THAO C/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2738" documentId="8_{00646CAE-D972-456C-BFFC-20763D0653A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC1BCEDF-C003-48D7-82F7-6A937EB0158C}"/>
+  <xr:revisionPtr revIDLastSave="2755" documentId="8_{00646CAE-D972-456C-BFFC-20763D0653A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A6BCCFA-ADE8-4CB8-BE69-C8A30C1D2893}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{98BF34B7-BF23-4246-A6AA-05D912D96073}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{98BF34B7-BF23-4246-A6AA-05D912D96073}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="10" r:id="rId1"/>
@@ -475,7 +475,7 @@
         max_by(s.t_db_mvmt_mth_lcl, STRUCT(s.source_event_date, s.load_timestamp)) AS t_db_mvmt_mth_lcl
     FROM cte_calendar c
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_pc_re_stat_line_bal') s
-        ON s.source_event_date &lt;= c.data_date
+        ON s.source_event_date = c.data_date
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_pc_re_stat_line_bal') h
         ON s.pc_re_stat_line_bal_hashkey = h.pc_re_stat_line_bal_hashkey
     LEFT JOIN gl_acct_dim g
@@ -2353,7 +2353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2588,6 +2588,267 @@
     <xf numFmtId="20" fontId="24" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2600,267 +2861,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2905,9 +2905,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3269,368 +3266,368 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:20" ht="33.75" customHeight="1">
-      <c r="B1" s="88" t="s">
+      <c r="B1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="89"/>
-      <c r="S1" s="89"/>
-      <c r="T1" s="89"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
+      <c r="K1" s="85"/>
+      <c r="L1" s="85"/>
+      <c r="M1" s="85"/>
+      <c r="N1" s="85"/>
+      <c r="O1" s="85"/>
+      <c r="P1" s="85"/>
+      <c r="Q1" s="85"/>
+      <c r="R1" s="85"/>
+      <c r="S1" s="85"/>
+      <c r="T1" s="85"/>
     </row>
     <row r="2" spans="2:20" ht="6" customHeight="1"/>
     <row r="3" spans="2:20" ht="21.75" customHeight="1">
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="148"/>
-      <c r="F3" s="146" t="s">
+      <c r="C3" s="143"/>
+      <c r="D3" s="144"/>
+      <c r="F3" s="142" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="147"/>
-      <c r="H3" s="148"/>
-      <c r="J3" s="149" t="s">
+      <c r="G3" s="143"/>
+      <c r="H3" s="144"/>
+      <c r="J3" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="150"/>
-      <c r="L3" s="151"/>
-      <c r="N3" s="149" t="s">
+      <c r="K3" s="146"/>
+      <c r="L3" s="147"/>
+      <c r="N3" s="145" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="150"/>
-      <c r="P3" s="151"/>
-      <c r="R3" s="137" t="s">
+      <c r="O3" s="146"/>
+      <c r="P3" s="147"/>
+      <c r="R3" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="S3" s="138"/>
-      <c r="T3" s="139"/>
+      <c r="S3" s="134"/>
+      <c r="T3" s="135"/>
     </row>
     <row r="4" spans="2:20" ht="6" customHeight="1"/>
     <row r="5" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="88" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="93"/>
-      <c r="D5" s="94"/>
-      <c r="F5" s="101" t="s">
+      <c r="C5" s="89"/>
+      <c r="D5" s="90"/>
+      <c r="F5" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="102"/>
-      <c r="H5" s="103"/>
-      <c r="J5" s="110" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="111"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="152" t="s">
+      <c r="G5" s="98"/>
+      <c r="H5" s="99"/>
+      <c r="J5" s="106" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="107"/>
+      <c r="L5" s="108"/>
+      <c r="M5" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="125" t="s">
+      <c r="N5" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="O5" s="126"/>
-      <c r="P5" s="127"/>
+      <c r="O5" s="122"/>
+      <c r="P5" s="123"/>
     </row>
     <row r="6" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="106"/>
-      <c r="J6" s="113"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="152"/>
-      <c r="N6" s="128"/>
-      <c r="O6" s="129"/>
-      <c r="P6" s="130"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="93"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="102"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="148"/>
+      <c r="N6" s="124"/>
+      <c r="O6" s="125"/>
+      <c r="P6" s="126"/>
       <c r="S6" s="37"/>
     </row>
     <row r="7" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B7" s="95"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="97"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="106"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="114"/>
-      <c r="L7" s="115"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="93"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="102"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="111"/>
       <c r="S7" s="37"/>
     </row>
     <row r="8" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B8" s="95"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="97"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="106"/>
-      <c r="J8" s="113"/>
-      <c r="K8" s="114"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="152" t="s">
+      <c r="B8" s="91"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="93"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="102"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="125" t="s">
+      <c r="N8" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="126"/>
-      <c r="P8" s="127"/>
+      <c r="O8" s="122"/>
+      <c r="P8" s="123"/>
     </row>
     <row r="9" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B9" s="95"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="97"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="106"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="114"/>
-      <c r="L9" s="115"/>
-      <c r="M9" s="152"/>
-      <c r="N9" s="128"/>
-      <c r="O9" s="129"/>
-      <c r="P9" s="130"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="93"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="102"/>
+      <c r="J9" s="109"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="148"/>
+      <c r="N9" s="124"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="126"/>
     </row>
     <row r="10" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B10" s="95"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="97"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="105"/>
-      <c r="H10" s="106"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="93"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="102"/>
       <c r="I10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="113"/>
-      <c r="K10" s="114"/>
-      <c r="L10" s="115"/>
+      <c r="J10" s="109"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="111"/>
     </row>
     <row r="11" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B11" s="95"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="97"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="106"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="114"/>
-      <c r="L11" s="115"/>
-      <c r="M11" s="152" t="s">
+      <c r="B11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="93"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="102"/>
+      <c r="J11" s="109"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="131" t="s">
+      <c r="N11" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="132"/>
-      <c r="P11" s="133"/>
-      <c r="Q11" s="152" t="s">
+      <c r="O11" s="128"/>
+      <c r="P11" s="129"/>
+      <c r="Q11" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="R11" s="131" t="s">
+      <c r="R11" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="S11" s="132"/>
-      <c r="T11" s="133"/>
+      <c r="S11" s="128"/>
+      <c r="T11" s="129"/>
     </row>
     <row r="12" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B12" s="95"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="97"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="106"/>
-      <c r="J12" s="113"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="115"/>
-      <c r="M12" s="152"/>
-      <c r="N12" s="134"/>
-      <c r="O12" s="135"/>
-      <c r="P12" s="136"/>
-      <c r="Q12" s="152"/>
-      <c r="R12" s="134"/>
-      <c r="S12" s="135"/>
-      <c r="T12" s="136"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="93"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="102"/>
+      <c r="J12" s="109"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="148"/>
+      <c r="N12" s="130"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="132"/>
+      <c r="Q12" s="148"/>
+      <c r="R12" s="130"/>
+      <c r="S12" s="131"/>
+      <c r="T12" s="132"/>
     </row>
     <row r="13" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B13" s="95"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="97"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="106"/>
-      <c r="J13" s="113"/>
-      <c r="K13" s="114"/>
-      <c r="L13" s="115"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="93"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="102"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="111"/>
     </row>
     <row r="14" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="97"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="93"/>
       <c r="E14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="104"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="106"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="114"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="152" t="s">
+      <c r="F14" s="100"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="102"/>
+      <c r="J14" s="109"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="N14" s="119" t="s">
+      <c r="N14" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="O14" s="120"/>
-      <c r="P14" s="121"/>
-      <c r="Q14" s="152" t="s">
+      <c r="O14" s="116"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="R14" s="140" t="s">
+      <c r="R14" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="141"/>
-      <c r="T14" s="142"/>
+      <c r="S14" s="137"/>
+      <c r="T14" s="138"/>
     </row>
     <row r="15" spans="2:20" ht="20.25" customHeight="1">
-      <c r="B15" s="95"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="97"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="106"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="118"/>
-      <c r="M15" s="152"/>
-      <c r="N15" s="122"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="124"/>
-      <c r="Q15" s="152"/>
-      <c r="R15" s="143"/>
-      <c r="S15" s="144"/>
-      <c r="T15" s="145"/>
+      <c r="B15" s="91"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="93"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="102"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="148"/>
+      <c r="N15" s="118"/>
+      <c r="O15" s="119"/>
+      <c r="P15" s="120"/>
+      <c r="Q15" s="148"/>
+      <c r="R15" s="139"/>
+      <c r="S15" s="140"/>
+      <c r="T15" s="141"/>
     </row>
     <row r="16" spans="2:20" ht="15" customHeight="1">
-      <c r="B16" s="95"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="97"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="106"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="93"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="101"/>
+      <c r="H16" s="102"/>
     </row>
     <row r="17" spans="2:16" ht="20.25" customHeight="1">
-      <c r="B17" s="95"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="97"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="106"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="93"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="101"/>
+      <c r="H17" s="102"/>
     </row>
     <row r="18" spans="2:16" ht="20.25" customHeight="1">
-      <c r="B18" s="95"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="97"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="152" t="s">
+      <c r="B18" s="91"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="93"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="J18" s="119" t="s">
+      <c r="J18" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="120"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="161" t="s">
+      <c r="K18" s="116"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="N18" s="131" t="s">
+      <c r="N18" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="O18" s="132"/>
-      <c r="P18" s="133"/>
+      <c r="O18" s="128"/>
+      <c r="P18" s="129"/>
     </row>
     <row r="19" spans="2:16" ht="20.25" customHeight="1">
-      <c r="B19" s="95"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="97"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="122"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="124"/>
-      <c r="M19" s="161"/>
-      <c r="N19" s="153"/>
-      <c r="O19" s="154"/>
-      <c r="P19" s="155"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="93"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="148"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="157"/>
+      <c r="N19" s="149"/>
+      <c r="O19" s="150"/>
+      <c r="P19" s="151"/>
     </row>
     <row r="20" spans="2:16" ht="10.5" customHeight="1">
-      <c r="B20" s="95"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="97"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="106"/>
-      <c r="N20" s="153"/>
-      <c r="O20" s="154"/>
-      <c r="P20" s="155"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="102"/>
+      <c r="N20" s="149"/>
+      <c r="O20" s="150"/>
+      <c r="P20" s="151"/>
     </row>
     <row r="21" spans="2:16" ht="20.25" customHeight="1">
-      <c r="B21" s="95"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="97"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="152" t="s">
+      <c r="B21" s="91"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="93"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="101"/>
+      <c r="H21" s="102"/>
+      <c r="I21" s="148" t="s">
         <v>9</v>
       </c>
-      <c r="J21" s="119" t="s">
+      <c r="J21" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="120"/>
-      <c r="L21" s="121"/>
-      <c r="M21" s="161" t="s">
+      <c r="K21" s="116"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="157" t="s">
         <v>9</v>
       </c>
-      <c r="N21" s="153"/>
-      <c r="O21" s="154"/>
-      <c r="P21" s="155"/>
+      <c r="N21" s="149"/>
+      <c r="O21" s="150"/>
+      <c r="P21" s="151"/>
     </row>
     <row r="22" spans="2:16" ht="20.25" customHeight="1">
-      <c r="B22" s="98"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="100"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="152"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="124"/>
-      <c r="M22" s="161"/>
-      <c r="N22" s="153"/>
-      <c r="O22" s="154"/>
-      <c r="P22" s="155"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="96"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="148"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="157"/>
+      <c r="N22" s="149"/>
+      <c r="O22" s="150"/>
+      <c r="P22" s="151"/>
     </row>
     <row r="23" spans="2:16" ht="20.25" customHeight="1"/>
     <row r="24" spans="2:16" ht="20.25" customHeight="1"/>
@@ -3638,11 +3635,11 @@
       <c r="B25" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="165" t="s">
+      <c r="J25" s="161" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="166"/>
-      <c r="L25" s="167"/>
+      <c r="K25" s="162"/>
+      <c r="L25" s="163"/>
       <c r="M25" s="79" t="s">
         <v>21</v>
       </c>
@@ -3651,21 +3648,21 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="20.25" customHeight="1">
-      <c r="B26" s="156"/>
-      <c r="C26" s="156"/>
-      <c r="D26" s="90" t="s">
+      <c r="B26" s="152"/>
+      <c r="C26" s="152"/>
+      <c r="D26" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="90"/>
-      <c r="J26" s="162" t="s">
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="158" t="s">
         <v>7</v>
       </c>
-      <c r="K26" s="163"/>
-      <c r="L26" s="164"/>
+      <c r="K26" s="159"/>
+      <c r="L26" s="160"/>
       <c r="M26" s="80" t="s">
         <v>24</v>
       </c>
@@ -3674,21 +3671,21 @@
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="157"/>
-      <c r="C27" s="157"/>
-      <c r="D27" s="90" t="s">
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="171" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="172"/>
-      <c r="L27" s="173"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="86"/>
+      <c r="H27" s="86"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="167" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="168"/>
+      <c r="L27" s="169"/>
       <c r="M27" s="80" t="s">
         <v>24</v>
       </c>
@@ -3697,21 +3694,21 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="158"/>
-      <c r="C28" s="158"/>
-      <c r="D28" s="90" t="s">
+      <c r="B28" s="154"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="90"/>
-      <c r="I28" s="90"/>
-      <c r="J28" s="174" t="s">
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="170" t="s">
         <v>16</v>
       </c>
-      <c r="K28" s="163"/>
-      <c r="L28" s="164"/>
+      <c r="K28" s="159"/>
+      <c r="L28" s="160"/>
       <c r="M28" s="80" t="s">
         <v>24</v>
       </c>
@@ -3720,21 +3717,21 @@
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="160"/>
-      <c r="C29" s="160"/>
-      <c r="D29" s="90" t="s">
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="90"/>
-      <c r="F29" s="90"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="90"/>
-      <c r="I29" s="90"/>
-      <c r="J29" s="168" t="s">
+      <c r="E29" s="86"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="86"/>
+      <c r="H29" s="86"/>
+      <c r="I29" s="86"/>
+      <c r="J29" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="K29" s="169"/>
-      <c r="L29" s="170"/>
+      <c r="K29" s="165"/>
+      <c r="L29" s="166"/>
       <c r="M29" s="80" t="s">
         <v>24</v>
       </c>
@@ -3743,21 +3740,21 @@
       </c>
     </row>
     <row r="30" spans="2:16" ht="18" customHeight="1">
-      <c r="B30" s="159"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="90" t="s">
+      <c r="B30" s="155"/>
+      <c r="C30" s="155"/>
+      <c r="D30" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="90"/>
-      <c r="F30" s="90"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="90"/>
-      <c r="I30" s="90"/>
-      <c r="J30" s="168" t="s">
+      <c r="E30" s="86"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="86"/>
+      <c r="J30" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="K30" s="169"/>
-      <c r="L30" s="170"/>
+      <c r="K30" s="165"/>
+      <c r="L30" s="166"/>
       <c r="M30" s="80" t="s">
         <v>24</v>
       </c>
@@ -3766,11 +3763,11 @@
       </c>
     </row>
     <row r="31" spans="2:16" ht="15" customHeight="1">
-      <c r="J31" s="168" t="s">
+      <c r="J31" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="K31" s="169"/>
-      <c r="L31" s="170"/>
+      <c r="K31" s="165"/>
+      <c r="L31" s="166"/>
       <c r="M31" s="80" t="s">
         <v>24</v>
       </c>
@@ -3779,11 +3776,11 @@
       </c>
     </row>
     <row r="32" spans="2:16" ht="15" customHeight="1">
-      <c r="J32" s="168" t="s">
+      <c r="J32" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="169"/>
-      <c r="L32" s="170"/>
+      <c r="K32" s="165"/>
+      <c r="L32" s="166"/>
       <c r="M32" s="80" t="s">
         <v>24</v>
       </c>
@@ -3951,7 +3948,7 @@
       <c r="B9" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="190" t="s">
+      <c r="C9" s="76" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3996,13 +3993,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.25" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1">
       <c r="A2" s="7" t="s">
@@ -4056,13 +4053,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="26.25" customHeight="1">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="173" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="87"/>
-      <c r="E6" s="87"/>
+      <c r="B6" s="174"/>
+      <c r="C6" s="174"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="174"/>
     </row>
     <row r="7" spans="1:5" ht="27.75" customHeight="1">
       <c r="A7" s="7" t="s">
@@ -8252,16 +8249,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8270,7 +8257,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -8442,14 +8429,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF058429-F5B4-4A8F-AEDD-B64B134BEA2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{921EC880-CEE1-4864-A95E-E1BCA8FFCF0E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{921EC880-CEE1-4864-A95E-E1BCA8FFCF0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CC24F18-6B81-4826-B056-559BAD924699}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CC24F18-6B81-4826-B056-559BAD924699}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF058429-F5B4-4A8F-AEDD-B64B134BEA2E}"/>
 </file>
--- a/input/mapping/027. OCB_GOLD_TCKH_V_SBV_BAOANH.xlsx
+++ b/input/mapping/027. OCB_GOLD_TCKH_V_SBV_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/THAO C/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2755" documentId="8_{00646CAE-D972-456C-BFFC-20763D0653A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A6BCCFA-ADE8-4CB8-BE69-C8A30C1D2893}"/>
+  <xr:revisionPtr revIDLastSave="2849" documentId="8_{00646CAE-D972-456C-BFFC-20763D0653A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A35CE384-B5BE-4E2A-90E7-882FC8C32F37}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{98BF34B7-BF23-4246-A6AA-05D912D96073}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="285">
   <si>
     <t>V_SBV   —   Data Lineage Mind Map</t>
   </si>
@@ -79,7 +79,12 @@
     <t>→</t>
   </si>
   <si>
-    <t>sbv_accountbc_save</t>
+    <t>hub_accountbc_save
+link_accountbc_save_account
+link_accountbc_save_branch
+sat_accountbc_save
+hub_account
+hub_branch</t>
   </si>
   <si>
     <t>sbv_accountbc_name</t>
@@ -431,7 +436,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+    <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
 CREATE OR REPLACE VIEW v_sbv_1 AS
 WITH w_data_date_full AS (
@@ -457,27 +462,93 @@
         msr_prd_dt AS data_date
     FROM IDENTIFIER(:cleaned || '.business_vault.calendar')
     WHERE msr_prd_dt &gt;= DATE '2026-01-01'
-      AND msr_prd_dt &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+      AND msr_prd_dt &lt;= TO_DATE(:target_date, 'yyyyMMdd')
+),
+cte_hub_account AS (
+    SELECT DISTINCT account_hashkey, business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account')
+),
+cte_hub_branch AS (
+    SELECT DISTINCT branch_hashkey, business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch')
+),
+cte_accountbc_save_sat AS (
+    SELECT
+        c.cdr_dt_id,
+        c.data_date,
+        h.accountbc_save_hashkey,
+        la.account_hashkey,
+        lb.branch_hashkey,
+        s.source_event_date,
+        s.ccy,
+        s.consolidate,
+        s.periodtype,
+        s.ddn,
+        s.ddc,
+        s.dsn,
+        s.dsc,
+        s.dcn,
+        s.dcc,
+        s.yetransfer
+    FROM cte_calendar c
+    INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_accountbc_save') h
+        ON h.source_event_date &lt;= c.data_date
+    INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.link_accountbc_save_account') la
+        ON la.accountbc_save_hashkey = h.accountbc_save_hashkey
+       AND la.source_event_date &lt;= c.data_date
+    INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.link_accountbc_save_branch') lb
+        ON lb.accountbc_save_hashkey = h.accountbc_save_hashkey
+       AND lb.source_event_date &lt;= c.data_date
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_accountbc_save') s
+        ON s.accountbc_save_hashkey = h.accountbc_save_hashkey
+       AND s.source_event_date &lt;= c.data_date
+    -- Lấy bản ghi hiệu lực mới nhất (theo source_event_date/load_timestamp/hashdiff) cho mỗi (ngày lịch, accountbc_save)
+    QUALIFY ROW_NUMBER() OVER (
+        PARTITION BY c.cdr_dt_id, h.accountbc_save_hashkey
+        ORDER BY la.source_event_date DESC, lb.source_event_date DESC,
+                 s.source_event_date DESC, s.load_timestamp DESC, s.hashdiff DESC
+    ) = 1
+),
+cte_accountbc_save AS (
+    SELECT
+        acc.cdr_dt_id,
+        acc.data_date,
+        acct_h.business_key AS account_id,
+        br_h.business_key   AS subbranch_id,
+        acc.ccy,
+        acc.consolidate,
+        acc.periodtype,
+        acc.ddn,
+        acc.ddc,
+        acc.dsn,
+        acc.dsc,
+        acc.dcn,
+        acc.dcc,
+        acc.yetransfer
+    FROM cte_accountbc_save_sat acc
+    INNER JOIN cte_hub_account acct_h
+        ON acct_h.account_hashkey = acc.account_hashkey
+    INNER JOIN cte_hub_branch br_h
+        ON br_h.branch_hashkey = acc.branch_hashkey
 ),
 cte_pc_re_stat_line_bal AS (
-    -- Giá trị Satellite mới nhất tính đến từng ngày snapshot (max_by thay QUALIFY ROW_NUMBER).
-    -- STRUCT(source_event_date, load_timestamp) để tie-break giống bản gốc.
     SELECT
         c.cdr_dt_id,
         c.data_date,
         h.business_key AS id,
         g.gl_nbr,
-        max_by(s.t_open_bal_lcl,    STRUCT(s.source_event_date, s.load_timestamp)) AS t_open_bal_lcl,
-        max_by(s.t_cr_mvmt_lcl,     STRUCT(s.source_event_date, s.load_timestamp)) AS t_cr_mvmt_lcl,
-        max_by(s.t_db_mvmt_lcl,     STRUCT(s.source_event_date, s.load_timestamp)) AS t_db_mvmt_lcl,
-        max_by(s.t_closing_bal_lcl, STRUCT(s.source_event_date, s.load_timestamp)) AS t_closing_bal_lcl,
-        max_by(s.t_cr_mvmt_mth_lcl, STRUCT(s.source_event_date, s.load_timestamp)) AS t_cr_mvmt_mth_lcl,
-        max_by(s.t_db_mvmt_mth_lcl, STRUCT(s.source_event_date, s.load_timestamp)) AS t_db_mvmt_mth_lcl
+        s.t_open_bal_lcl,
+        s.t_cr_mvmt_lcl,
+        s.t_db_mvmt_lcl,
+        s.t_closing_bal_lcl,
+        s.t_cr_mvmt_mth_lcl,
+        s.t_db_mvmt_mth_lcl
     FROM cte_calendar c
-    INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_pc_re_stat_line_bal') s
-        ON s.source_event_date = c.data_date
     INNER JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_pc_re_stat_line_bal') h
+        ON h.source_event_date = c.data_date
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_pc_re_stat_line_bal') s
         ON s.pc_re_stat_line_bal_hashkey = h.pc_re_stat_line_bal_hashkey
+       AND s.source_event_date = c.data_date
     LEFT JOIN gl_acct_dim g
         ON SUBSTRING(h.business_key, 11, 4) = CAST(g.line_nbr AS STRING)
     WHERE h.business_key NOT LIKE '%LOCAL%'
@@ -489,12 +560,16 @@
                 '7905', '7908', '7909', '8832', '8929'
             )
       )
-    GROUP BY c.cdr_dt_id, c.data_date, h.business_key, g.gl_nbr
+    -- Lấy bản ghi số dư mới nhất (theo source_event_date/load_timestamp/hashdiff) cho mỗi (ngày lịch, business_key, gl_nbr)
+    QUALIFY ROW_NUMBER() OVER (
+        PARTITION BY c.cdr_dt_id, c.data_date, h.business_key, g.gl_nbr
+        ORDER BY s.source_event_date DESC, s.load_timestamp DESC, s.hashdiff DESC
+    ) = 1
 )
 -- Block 1: dữ liệu SBV gốc
 SELECT
-    b.data_dt                                    AS cdr_dt_id,
-    b.data_date_dt                               AS data_date,
+    d.holiday_dt                                 AS cdr_dt_id,
+    d.data_date_dt                               AS data_date,
     CAST(a.account_id AS STRING)                 AS gl,
     CONCAT(CAST(a.account_id AS STRING), '0')    AS line,
     a.subbranch_id                               AS subbranch_id,
@@ -511,11 +586,11 @@
     CAST(NULL AS DECIMAL(23,4))                  AS t_cr_mvmt_lcl,
     CAST(NULL AS DECIMAL(23,4))                  AS t_db_mvmt_lcl,
     CAST(NULL AS DECIMAL(23,4))                  AS t_closing_bal_lcl,
-    n.name                                       AS account_name,
+    n.name                                        AS account_name,
     a.yetransfer                                 AS yetransfer
-FROM sbv_accountbc_save a
-LEFT JOIN w_data_date_full b
-    ON CAST(a.data_date AS STRING) = CAST(b.holiday_dt AS STRING)
+FROM cte_accountbc_save a
+LEFT JOIN w_data_date_full d
+    ON a.data_date = d.holiday_date_dt
 LEFT JOIN sbv_accountbc_name n
     ON a.account_id = n.account_id
 WHERE a.yetransfer &lt;&gt; 'AF'
@@ -612,20 +687,13 @@
     -b.t_cr_mvmt_mth_lcl                         AS t_cr_mvmt_lcl,
     -b.t_db_mvmt_mth_lcl                         AS t_db_mvmt_lcl,
     -b.t_closing_bal_lcl                         AS t_closing_bal_lcl,
-    ''                                            AS account_name,
-    ''                                            AS yetransfer
-FROM cte_pc_re_stat_line_bal b;
-</t>
+    ''                                           AS account_name,
+    ''                                           AS yetransfer
+FROM cte_pc_re_stat_line_bal b;</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS GL_ACCT_DIM (
-    DSC         STRING,
-    GL_NBR      INT,
-    LINE_NBR    INT
-)
-USING DELTA;
 TRUNCATE TABLE GL_ACCT_DIM;
 INSERT INTO GL_ACCT_DIM (
     DSC, GL_NBR, LINE_NBR
@@ -649,9 +717,14 @@
 </t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE holiday AS
+INSERT OVERWRITE holiday (
+    DATA_DATE_DT,
+    HOLIDAY_DATE_DT,
+    DATA_DT,
+    HOLIDAY_DT
+)
 SELECT
     TO_DATE(CAST(MAX(W.msr_prd_id) AS STRING), 'yyyyMMdd')   AS DATA_DATE_DT,
     TO_DATE(CAST(D.msr_prd_id AS STRING), 'yyyyMMdd')        AS HOLIDAY_DATE_DT,
@@ -662,12 +735,21 @@
     ON  D.msr_prd_id &gt; W.msr_prd_id
     AND W.bsn_day_f = 1
 WHERE D.bsn_day_f = 0
-GROUP BY D.msr_prd_id;</t>
+GROUP BY D.msr_prd_id;
+</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE working_day AS
+INSERT OVERWRITE working_day (
+    DATA_DT,
+    FROM_DATE_DT,
+    FROM_DT,
+    END_DT,
+    END_DATE_DT,
+    BEGIN_OF_MONTH,
+    BEGIN_OF_MONTH_DATE
+)
 WITH
 v_from_dt AS (
     SELECT
@@ -968,6 +1050,9 @@
     <t>Note</t>
   </si>
   <si>
+    <t>sbv_accountbc_save</t>
+  </si>
+  <si>
     <t xml:space="preserve">A </t>
   </si>
   <si>
@@ -1547,7 +1632,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1692,6 +1777,11 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="14">
@@ -2353,7 +2443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2699,6 +2789,24 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2717,22 +2825,22 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2744,22 +2852,22 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2783,13 +2891,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3290,34 +3398,34 @@
     </row>
     <row r="2" spans="2:20" ht="6" customHeight="1"/>
     <row r="3" spans="2:20" ht="21.75" customHeight="1">
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143"/>
-      <c r="D3" s="144"/>
-      <c r="F3" s="142" t="s">
+      <c r="C3" s="149"/>
+      <c r="D3" s="150"/>
+      <c r="F3" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="143"/>
-      <c r="H3" s="144"/>
-      <c r="J3" s="145" t="s">
+      <c r="G3" s="149"/>
+      <c r="H3" s="150"/>
+      <c r="J3" s="151" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="146"/>
-      <c r="L3" s="147"/>
-      <c r="N3" s="145" t="s">
+      <c r="K3" s="152"/>
+      <c r="L3" s="153"/>
+      <c r="N3" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="146"/>
-      <c r="P3" s="147"/>
-      <c r="R3" s="133" t="s">
+      <c r="O3" s="152"/>
+      <c r="P3" s="153"/>
+      <c r="R3" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="S3" s="134"/>
-      <c r="T3" s="135"/>
+      <c r="S3" s="140"/>
+      <c r="T3" s="141"/>
     </row>
     <row r="4" spans="2:20" ht="6" customHeight="1"/>
-    <row r="5" spans="2:20" ht="20.25" customHeight="1">
+    <row r="5" spans="2:20" ht="46.5" customHeight="1">
       <c r="B5" s="88" t="s">
         <v>6</v>
       </c>
@@ -3333,7 +3441,7 @@
       </c>
       <c r="K5" s="107"/>
       <c r="L5" s="108"/>
-      <c r="M5" s="148" t="s">
+      <c r="M5" s="154" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="121" t="s">
@@ -3342,7 +3450,7 @@
       <c r="O5" s="122"/>
       <c r="P5" s="123"/>
     </row>
-    <row r="6" spans="2:20" ht="20.25" customHeight="1">
+    <row r="6" spans="2:20" ht="50.25" customHeight="1">
       <c r="B6" s="91"/>
       <c r="C6" s="92"/>
       <c r="D6" s="93"/>
@@ -3352,7 +3460,7 @@
       <c r="J6" s="109"/>
       <c r="K6" s="110"/>
       <c r="L6" s="111"/>
-      <c r="M6" s="148"/>
+      <c r="M6" s="154"/>
       <c r="N6" s="124"/>
       <c r="O6" s="125"/>
       <c r="P6" s="126"/>
@@ -3380,14 +3488,14 @@
       <c r="J8" s="109"/>
       <c r="K8" s="110"/>
       <c r="L8" s="111"/>
-      <c r="M8" s="148" t="s">
+      <c r="M8" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="121" t="s">
+      <c r="N8" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="122"/>
-      <c r="P8" s="123"/>
+      <c r="O8" s="128"/>
+      <c r="P8" s="129"/>
     </row>
     <row r="9" spans="2:20" ht="20.25" customHeight="1">
       <c r="B9" s="91"/>
@@ -3399,10 +3507,10 @@
       <c r="J9" s="109"/>
       <c r="K9" s="110"/>
       <c r="L9" s="111"/>
-      <c r="M9" s="148"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="125"/>
-      <c r="P9" s="126"/>
+      <c r="M9" s="154"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="132"/>
     </row>
     <row r="10" spans="2:20" ht="20.25" customHeight="1">
       <c r="B10" s="91"/>
@@ -3428,22 +3536,22 @@
       <c r="J11" s="109"/>
       <c r="K11" s="110"/>
       <c r="L11" s="111"/>
-      <c r="M11" s="148" t="s">
+      <c r="M11" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="127" t="s">
+      <c r="N11" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="128"/>
-      <c r="P11" s="129"/>
-      <c r="Q11" s="148" t="s">
+      <c r="O11" s="134"/>
+      <c r="P11" s="135"/>
+      <c r="Q11" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="R11" s="127" t="s">
+      <c r="R11" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="S11" s="128"/>
-      <c r="T11" s="129"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="135"/>
     </row>
     <row r="12" spans="2:20" ht="20.25" customHeight="1">
       <c r="B12" s="91"/>
@@ -3455,14 +3563,14 @@
       <c r="J12" s="109"/>
       <c r="K12" s="110"/>
       <c r="L12" s="111"/>
-      <c r="M12" s="148"/>
-      <c r="N12" s="130"/>
-      <c r="O12" s="131"/>
-      <c r="P12" s="132"/>
-      <c r="Q12" s="148"/>
-      <c r="R12" s="130"/>
-      <c r="S12" s="131"/>
-      <c r="T12" s="132"/>
+      <c r="M12" s="154"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="137"/>
+      <c r="P12" s="138"/>
+      <c r="Q12" s="154"/>
+      <c r="R12" s="136"/>
+      <c r="S12" s="137"/>
+      <c r="T12" s="138"/>
     </row>
     <row r="13" spans="2:20" ht="20.25" customHeight="1">
       <c r="B13" s="91"/>
@@ -3488,7 +3596,7 @@
       <c r="J14" s="109"/>
       <c r="K14" s="110"/>
       <c r="L14" s="111"/>
-      <c r="M14" s="148" t="s">
+      <c r="M14" s="154" t="s">
         <v>9</v>
       </c>
       <c r="N14" s="115" t="s">
@@ -3496,14 +3604,14 @@
       </c>
       <c r="O14" s="116"/>
       <c r="P14" s="117"/>
-      <c r="Q14" s="148" t="s">
+      <c r="Q14" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="R14" s="136" t="s">
+      <c r="R14" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="137"/>
-      <c r="T14" s="138"/>
+      <c r="S14" s="143"/>
+      <c r="T14" s="144"/>
     </row>
     <row r="15" spans="2:20" ht="20.25" customHeight="1">
       <c r="B15" s="91"/>
@@ -3515,14 +3623,14 @@
       <c r="J15" s="112"/>
       <c r="K15" s="113"/>
       <c r="L15" s="114"/>
-      <c r="M15" s="148"/>
+      <c r="M15" s="154"/>
       <c r="N15" s="118"/>
       <c r="O15" s="119"/>
       <c r="P15" s="120"/>
-      <c r="Q15" s="148"/>
-      <c r="R15" s="139"/>
-      <c r="S15" s="140"/>
-      <c r="T15" s="141"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="145"/>
+      <c r="S15" s="146"/>
+      <c r="T15" s="147"/>
     </row>
     <row r="16" spans="2:20" ht="15" customHeight="1">
       <c r="B16" s="91"/>
@@ -3547,7 +3655,7 @@
       <c r="F18" s="100"/>
       <c r="G18" s="101"/>
       <c r="H18" s="102"/>
-      <c r="I18" s="148" t="s">
+      <c r="I18" s="154" t="s">
         <v>9</v>
       </c>
       <c r="J18" s="115" t="s">
@@ -3555,14 +3663,14 @@
       </c>
       <c r="K18" s="116"/>
       <c r="L18" s="117"/>
-      <c r="M18" s="157" t="s">
+      <c r="M18" s="163" t="s">
         <v>9</v>
       </c>
-      <c r="N18" s="127" t="s">
+      <c r="N18" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="O18" s="128"/>
-      <c r="P18" s="129"/>
+      <c r="O18" s="134"/>
+      <c r="P18" s="135"/>
     </row>
     <row r="19" spans="2:16" ht="20.25" customHeight="1">
       <c r="B19" s="91"/>
@@ -3571,14 +3679,14 @@
       <c r="F19" s="100"/>
       <c r="G19" s="101"/>
       <c r="H19" s="102"/>
-      <c r="I19" s="148"/>
+      <c r="I19" s="154"/>
       <c r="J19" s="118"/>
       <c r="K19" s="119"/>
       <c r="L19" s="120"/>
-      <c r="M19" s="157"/>
-      <c r="N19" s="149"/>
-      <c r="O19" s="150"/>
-      <c r="P19" s="151"/>
+      <c r="M19" s="163"/>
+      <c r="N19" s="155"/>
+      <c r="O19" s="156"/>
+      <c r="P19" s="157"/>
     </row>
     <row r="20" spans="2:16" ht="10.5" customHeight="1">
       <c r="B20" s="91"/>
@@ -3587,9 +3695,9 @@
       <c r="F20" s="100"/>
       <c r="G20" s="101"/>
       <c r="H20" s="102"/>
-      <c r="N20" s="149"/>
-      <c r="O20" s="150"/>
-      <c r="P20" s="151"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="156"/>
+      <c r="P20" s="157"/>
     </row>
     <row r="21" spans="2:16" ht="20.25" customHeight="1">
       <c r="B21" s="91"/>
@@ -3598,7 +3706,7 @@
       <c r="F21" s="100"/>
       <c r="G21" s="101"/>
       <c r="H21" s="102"/>
-      <c r="I21" s="148" t="s">
+      <c r="I21" s="154" t="s">
         <v>9</v>
       </c>
       <c r="J21" s="115" t="s">
@@ -3606,12 +3714,12 @@
       </c>
       <c r="K21" s="116"/>
       <c r="L21" s="117"/>
-      <c r="M21" s="157" t="s">
+      <c r="M21" s="163" t="s">
         <v>9</v>
       </c>
-      <c r="N21" s="149"/>
-      <c r="O21" s="150"/>
-      <c r="P21" s="151"/>
+      <c r="N21" s="155"/>
+      <c r="O21" s="156"/>
+      <c r="P21" s="157"/>
     </row>
     <row r="22" spans="2:16" ht="20.25" customHeight="1">
       <c r="B22" s="94"/>
@@ -3620,14 +3728,14 @@
       <c r="F22" s="103"/>
       <c r="G22" s="104"/>
       <c r="H22" s="105"/>
-      <c r="I22" s="148"/>
+      <c r="I22" s="154"/>
       <c r="J22" s="118"/>
       <c r="K22" s="119"/>
       <c r="L22" s="120"/>
-      <c r="M22" s="157"/>
-      <c r="N22" s="149"/>
-      <c r="O22" s="150"/>
-      <c r="P22" s="151"/>
+      <c r="M22" s="163"/>
+      <c r="N22" s="155"/>
+      <c r="O22" s="156"/>
+      <c r="P22" s="157"/>
     </row>
     <row r="23" spans="2:16" ht="20.25" customHeight="1"/>
     <row r="24" spans="2:16" ht="20.25" customHeight="1"/>
@@ -3635,11 +3743,11 @@
       <c r="B25" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="161" t="s">
+      <c r="J25" s="167" t="s">
         <v>20</v>
       </c>
-      <c r="K25" s="162"/>
-      <c r="L25" s="163"/>
+      <c r="K25" s="168"/>
+      <c r="L25" s="169"/>
       <c r="M25" s="79" t="s">
         <v>21</v>
       </c>
@@ -3648,8 +3756,8 @@
       </c>
     </row>
     <row r="26" spans="2:16" ht="20.25" customHeight="1">
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
+      <c r="B26" s="158"/>
+      <c r="C26" s="158"/>
       <c r="D26" s="86" t="s">
         <v>23</v>
       </c>
@@ -3658,11 +3766,11 @@
       <c r="G26" s="86"/>
       <c r="H26" s="86"/>
       <c r="I26" s="86"/>
-      <c r="J26" s="158" t="s">
+      <c r="J26" s="164" t="s">
         <v>7</v>
       </c>
-      <c r="K26" s="159"/>
-      <c r="L26" s="160"/>
+      <c r="K26" s="165"/>
+      <c r="L26" s="166"/>
       <c r="M26" s="80" t="s">
         <v>24</v>
       </c>
@@ -3671,8 +3779,8 @@
       </c>
     </row>
     <row r="27" spans="2:16">
-      <c r="B27" s="153"/>
-      <c r="C27" s="153"/>
+      <c r="B27" s="159"/>
+      <c r="C27" s="159"/>
       <c r="D27" s="86" t="s">
         <v>25</v>
       </c>
@@ -3681,11 +3789,11 @@
       <c r="G27" s="86"/>
       <c r="H27" s="86"/>
       <c r="I27" s="87"/>
-      <c r="J27" s="167" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="168"/>
-      <c r="L27" s="169"/>
+      <c r="J27" s="173" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="174"/>
+      <c r="L27" s="175"/>
       <c r="M27" s="80" t="s">
         <v>24</v>
       </c>
@@ -3694,8 +3802,8 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
+      <c r="B28" s="160"/>
+      <c r="C28" s="160"/>
       <c r="D28" s="86" t="s">
         <v>26</v>
       </c>
@@ -3704,11 +3812,11 @@
       <c r="G28" s="86"/>
       <c r="H28" s="86"/>
       <c r="I28" s="86"/>
-      <c r="J28" s="170" t="s">
+      <c r="J28" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="K28" s="159"/>
-      <c r="L28" s="160"/>
+      <c r="K28" s="165"/>
+      <c r="L28" s="166"/>
       <c r="M28" s="80" t="s">
         <v>24</v>
       </c>
@@ -3717,8 +3825,8 @@
       </c>
     </row>
     <row r="29" spans="2:16">
-      <c r="B29" s="156"/>
-      <c r="C29" s="156"/>
+      <c r="B29" s="162"/>
+      <c r="C29" s="162"/>
       <c r="D29" s="86" t="s">
         <v>27</v>
       </c>
@@ -3727,11 +3835,11 @@
       <c r="G29" s="86"/>
       <c r="H29" s="86"/>
       <c r="I29" s="86"/>
-      <c r="J29" s="164" t="s">
+      <c r="J29" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="K29" s="165"/>
-      <c r="L29" s="166"/>
+      <c r="K29" s="171"/>
+      <c r="L29" s="172"/>
       <c r="M29" s="80" t="s">
         <v>24</v>
       </c>
@@ -3740,8 +3848,8 @@
       </c>
     </row>
     <row r="30" spans="2:16" ht="18" customHeight="1">
-      <c r="B30" s="155"/>
-      <c r="C30" s="155"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="161"/>
       <c r="D30" s="86" t="s">
         <v>28</v>
       </c>
@@ -3750,11 +3858,11 @@
       <c r="G30" s="86"/>
       <c r="H30" s="86"/>
       <c r="I30" s="86"/>
-      <c r="J30" s="164" t="s">
+      <c r="J30" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="K30" s="165"/>
-      <c r="L30" s="166"/>
+      <c r="K30" s="171"/>
+      <c r="L30" s="172"/>
       <c r="M30" s="80" t="s">
         <v>24</v>
       </c>
@@ -3763,11 +3871,11 @@
       </c>
     </row>
     <row r="31" spans="2:16" ht="15" customHeight="1">
-      <c r="J31" s="164" t="s">
+      <c r="J31" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="K31" s="165"/>
-      <c r="L31" s="166"/>
+      <c r="K31" s="171"/>
+      <c r="L31" s="172"/>
       <c r="M31" s="80" t="s">
         <v>24</v>
       </c>
@@ -3776,11 +3884,11 @@
       </c>
     </row>
     <row r="32" spans="2:16" ht="15" customHeight="1">
-      <c r="J32" s="164" t="s">
+      <c r="J32" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="K32" s="165"/>
-      <c r="L32" s="166"/>
+      <c r="K32" s="171"/>
+      <c r="L32" s="172"/>
       <c r="M32" s="80" t="s">
         <v>24</v>
       </c>
@@ -3993,13 +4101,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="32.25" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="177" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
     </row>
     <row r="2" spans="1:5" ht="20.25" customHeight="1">
       <c r="A2" s="7" t="s">
@@ -4053,13 +4161,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="26.25" customHeight="1">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="179" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
-      <c r="E6" s="174"/>
+      <c r="B6" s="180"/>
+      <c r="C6" s="180"/>
+      <c r="D6" s="180"/>
+      <c r="E6" s="180"/>
     </row>
     <row r="7" spans="1:5" ht="27.75" customHeight="1">
       <c r="A7" s="7" t="s">
@@ -4529,15 +4637,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="184" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="180"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="185"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="186"/>
     </row>
     <row r="2" spans="1:7" ht="23.25" customHeight="1">
       <c r="A2" s="38" t="s">
@@ -4567,22 +4675,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D3" s="40" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G3" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="163.5" customHeight="1">
@@ -4590,22 +4698,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D4" s="40" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F4" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G4" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="31.5" customHeight="1">
@@ -4616,19 +4724,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D5" s="40" t="s">
         <v>61</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F5" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="132.75" customHeight="1">
@@ -4636,22 +4744,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="408.75" customHeight="1">
@@ -4659,17 +4767,17 @@
         <v>5</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="40" t="s">
         <v>60</v>
       </c>
       <c r="D7" s="40" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E7" s="40"/>
       <c r="F7" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G7" s="40"/>
     </row>
@@ -4678,19 +4786,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E8" s="40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G8" s="40"/>
     </row>
@@ -4699,19 +4807,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D9" s="40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E9" s="40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G9" s="40"/>
     </row>
@@ -4723,16 +4831,16 @@
         <v>14</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10" s="40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G10" s="40"/>
     </row>
@@ -4755,15 +4863,15 @@
       <c r="G12" s="44"/>
     </row>
     <row r="13" spans="1:7" ht="23.25" customHeight="1">
-      <c r="A13" s="175" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="176"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="176"/>
-      <c r="G13" s="177"/>
+      <c r="A13" s="181" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="183"/>
     </row>
     <row r="14" spans="1:7" ht="43.5" customHeight="1">
       <c r="A14" s="38" t="s">
@@ -4779,25 +4887,25 @@
         <v>66</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>121</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A15" s="175" t="s">
-        <v>153</v>
-      </c>
-      <c r="B15" s="176"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
-      <c r="E15" s="176"/>
-      <c r="F15" s="176"/>
-      <c r="G15" s="177"/>
+      <c r="A15" s="181" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="182"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="182"/>
+      <c r="E15" s="182"/>
+      <c r="F15" s="182"/>
+      <c r="G15" s="183"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="39" t="s">
@@ -4810,16 +4918,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G16" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4833,16 +4941,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D17" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E17" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="40" t="s">
-        <v>155</v>
-      </c>
       <c r="F17" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G17" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4856,16 +4964,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G18" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4876,19 +4984,19 @@
         <v>75</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E19" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4905,13 +5013,13 @@
         <v>78</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F20" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G20" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4928,13 +5036,13 @@
         <v>80</v>
       </c>
       <c r="E21" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G21" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4951,13 +5059,13 @@
         <v>82</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F22" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G22" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4974,13 +5082,13 @@
         <v>84</v>
       </c>
       <c r="E23" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G23" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4997,13 +5105,13 @@
         <v>86</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F24" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G24" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5020,13 +5128,13 @@
         <v>88</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G25" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5040,16 +5148,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G26" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -5063,16 +5171,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D27" s="40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G27" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -5089,13 +5197,13 @@
         <v>100</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F28" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G28" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5112,13 +5220,13 @@
         <v>102</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F29" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G29" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5129,19 +5237,19 @@
         <v>103</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D30" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E30" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="40" t="s">
-        <v>126</v>
-      </c>
       <c r="G30" s="40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5152,19 +5260,19 @@
         <v>105</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D31" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E31" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="40" t="s">
-        <v>126</v>
-      </c>
       <c r="G31" s="40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5175,19 +5283,19 @@
         <v>107</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D32" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E32" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="40" t="s">
-        <v>126</v>
-      </c>
       <c r="G32" s="40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5198,19 +5306,19 @@
         <v>113</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D33" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E33" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="F33" s="40" t="s">
-        <v>126</v>
-      </c>
       <c r="G33" s="40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5224,16 +5332,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34" s="40" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G34" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -5250,25 +5358,25 @@
         <v>118</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G35" s="40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A36" s="175" t="s">
-        <v>167</v>
-      </c>
-      <c r="B36" s="176"/>
-      <c r="C36" s="176"/>
-      <c r="D36" s="176"/>
-      <c r="E36" s="176"/>
-      <c r="F36" s="176"/>
-      <c r="G36" s="177"/>
+      <c r="A36" s="181" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="182"/>
+      <c r="C36" s="182"/>
+      <c r="D36" s="182"/>
+      <c r="E36" s="182"/>
+      <c r="F36" s="182"/>
+      <c r="G36" s="183"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="39" t="s">
@@ -5278,16 +5386,16 @@
         <v>68</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D37" s="40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F37" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G37" s="40"/>
     </row>
@@ -5299,16 +5407,16 @@
         <v>71</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D38" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="40" t="s">
         <v>171</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F38" s="40" t="s">
-        <v>170</v>
       </c>
       <c r="G38" s="40"/>
     </row>
@@ -5320,16 +5428,16 @@
         <v>73</v>
       </c>
       <c r="C39" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D39" s="40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F39" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G39" s="40"/>
     </row>
@@ -5341,19 +5449,19 @@
         <v>75</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G40" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -5364,19 +5472,19 @@
         <v>77</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D41" s="40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F41" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G41" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -5387,19 +5495,19 @@
         <v>79</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G42" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -5410,19 +5518,19 @@
         <v>81</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G43" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5433,19 +5541,19 @@
         <v>83</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E44" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G44" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -5456,19 +5564,19 @@
         <v>85</v>
       </c>
       <c r="C45" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D45" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G45" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -5479,19 +5587,19 @@
         <v>87</v>
       </c>
       <c r="C46" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G46" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5502,19 +5610,19 @@
         <v>89</v>
       </c>
       <c r="C47" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D47" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E47" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F47" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G47" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5525,19 +5633,19 @@
         <v>93</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D48" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E48" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G48" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5548,19 +5656,19 @@
         <v>99</v>
       </c>
       <c r="C49" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D49" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E49" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F49" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G49" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5571,19 +5679,19 @@
         <v>101</v>
       </c>
       <c r="C50" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E50" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G50" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5597,16 +5705,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D51" s="40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F51" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G51" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5620,16 +5728,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G52" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5643,16 +5751,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F53" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G53" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5666,16 +5774,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G54" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5686,19 +5794,19 @@
         <v>115</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E55" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G55" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5709,31 +5817,31 @@
         <v>117</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D56" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E56" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G56" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A57" s="175" t="s">
-        <v>183</v>
-      </c>
-      <c r="B57" s="176"/>
-      <c r="C57" s="176"/>
-      <c r="D57" s="176"/>
-      <c r="E57" s="176"/>
-      <c r="F57" s="176"/>
-      <c r="G57" s="177"/>
+      <c r="A57" s="181" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="182"/>
+      <c r="C57" s="182"/>
+      <c r="D57" s="182"/>
+      <c r="E57" s="182"/>
+      <c r="F57" s="182"/>
+      <c r="G57" s="183"/>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="39" t="s">
@@ -5743,16 +5851,16 @@
         <v>68</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F58" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G58" s="40"/>
     </row>
@@ -5764,16 +5872,16 @@
         <v>71</v>
       </c>
       <c r="C59" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D59" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="E59" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F59" s="40" t="s">
         <v>185</v>
-      </c>
-      <c r="E59" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F59" s="40" t="s">
-        <v>184</v>
       </c>
       <c r="G59" s="40"/>
     </row>
@@ -5785,16 +5893,16 @@
         <v>73</v>
       </c>
       <c r="C60" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F60" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G60" s="40"/>
     </row>
@@ -5806,19 +5914,19 @@
         <v>75</v>
       </c>
       <c r="C61" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F61" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G61" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5829,19 +5937,19 @@
         <v>77</v>
       </c>
       <c r="C62" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E62" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F62" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G62" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5852,19 +5960,19 @@
         <v>79</v>
       </c>
       <c r="C63" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D63" s="40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F63" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G63" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5875,19 +5983,19 @@
         <v>81</v>
       </c>
       <c r="C64" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E64" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F64" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G64" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5898,19 +6006,19 @@
         <v>83</v>
       </c>
       <c r="C65" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E65" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F65" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G65" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5921,19 +6029,19 @@
         <v>85</v>
       </c>
       <c r="C66" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E66" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F66" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G66" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5944,19 +6052,19 @@
         <v>87</v>
       </c>
       <c r="C67" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E67" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F67" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G67" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5967,19 +6075,19 @@
         <v>89</v>
       </c>
       <c r="C68" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D68" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E68" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F68" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G68" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5990,19 +6098,19 @@
         <v>93</v>
       </c>
       <c r="C69" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D69" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E69" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F69" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G69" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -6013,19 +6121,19 @@
         <v>99</v>
       </c>
       <c r="C70" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D70" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E70" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F70" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G70" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -6036,19 +6144,19 @@
         <v>101</v>
       </c>
       <c r="C71" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D71" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E71" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F71" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G71" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -6062,16 +6170,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D72" s="40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F72" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G72" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -6082,19 +6190,19 @@
         <v>105</v>
       </c>
       <c r="C73" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D73" s="40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E73" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F73" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G73" s="40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -6105,19 +6213,19 @@
         <v>107</v>
       </c>
       <c r="C74" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D74" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E74" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F74" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="G74" s="40" t="s">
         <v>189</v>
-      </c>
-      <c r="E74" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F74" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="G74" s="40" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -6131,16 +6239,16 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="D75" s="40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F75" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G75" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -6151,19 +6259,19 @@
         <v>115</v>
       </c>
       <c r="C76" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D76" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F76" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G76" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -6174,31 +6282,31 @@
         <v>117</v>
       </c>
       <c r="C77" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D77" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E77" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F77" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G77" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A78" s="175" t="s">
-        <v>190</v>
-      </c>
-      <c r="B78" s="176"/>
-      <c r="C78" s="176"/>
-      <c r="D78" s="176"/>
-      <c r="E78" s="176"/>
-      <c r="F78" s="176"/>
-      <c r="G78" s="177"/>
+      <c r="A78" s="181" t="s">
+        <v>191</v>
+      </c>
+      <c r="B78" s="182"/>
+      <c r="C78" s="182"/>
+      <c r="D78" s="182"/>
+      <c r="E78" s="182"/>
+      <c r="F78" s="182"/>
+      <c r="G78" s="183"/>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="39" t="s">
@@ -6208,16 +6316,16 @@
         <v>68</v>
       </c>
       <c r="C79" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D79" s="40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E79" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F79" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G79" s="40"/>
     </row>
@@ -6229,16 +6337,16 @@
         <v>71</v>
       </c>
       <c r="C80" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D80" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="E80" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" s="40" t="s">
         <v>192</v>
-      </c>
-      <c r="E80" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F80" s="40" t="s">
-        <v>191</v>
       </c>
       <c r="G80" s="40"/>
     </row>
@@ -6250,16 +6358,16 @@
         <v>73</v>
       </c>
       <c r="C81" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D81" s="40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F81" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G81" s="40"/>
     </row>
@@ -6271,16 +6379,16 @@
         <v>75</v>
       </c>
       <c r="C82" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D82" s="40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F82" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G82" s="40"/>
     </row>
@@ -6292,19 +6400,19 @@
         <v>77</v>
       </c>
       <c r="C83" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D83" s="40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E83" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F83" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G83" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6315,19 +6423,19 @@
         <v>79</v>
       </c>
       <c r="C84" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D84" s="40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E84" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F84" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G84" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6338,19 +6446,19 @@
         <v>81</v>
       </c>
       <c r="C85" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D85" s="40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E85" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F85" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G85" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6361,19 +6469,19 @@
         <v>83</v>
       </c>
       <c r="C86" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D86" s="40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E86" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F86" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G86" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6384,19 +6492,19 @@
         <v>85</v>
       </c>
       <c r="C87" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D87" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E87" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F87" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G87" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6407,19 +6515,19 @@
         <v>87</v>
       </c>
       <c r="C88" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D88" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E88" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F88" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G88" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6430,19 +6538,19 @@
         <v>89</v>
       </c>
       <c r="C89" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D89" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E89" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F89" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G89" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6453,19 +6561,19 @@
         <v>93</v>
       </c>
       <c r="C90" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D90" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E90" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F90" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G90" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6476,19 +6584,19 @@
         <v>99</v>
       </c>
       <c r="C91" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D91" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E91" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F91" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G91" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6499,19 +6607,19 @@
         <v>101</v>
       </c>
       <c r="C92" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D92" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E92" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F92" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G92" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6522,19 +6630,19 @@
         <v>103</v>
       </c>
       <c r="C93" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D93" s="41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F93" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6545,19 +6653,19 @@
         <v>105</v>
       </c>
       <c r="C94" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D94" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="E94" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F94" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="G94" s="40" t="s">
         <v>196</v>
-      </c>
-      <c r="E94" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F94" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="G94" s="40" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6568,19 +6676,19 @@
         <v>107</v>
       </c>
       <c r="C95" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D95" s="41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F95" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G95" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6591,19 +6699,19 @@
         <v>113</v>
       </c>
       <c r="C96" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D96" s="41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F96" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G96" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6614,19 +6722,19 @@
         <v>115</v>
       </c>
       <c r="C97" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D97" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E97" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F97" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G97" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6637,31 +6745,31 @@
         <v>117</v>
       </c>
       <c r="C98" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D98" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E98" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F98" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G98" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A99" s="175" t="s">
-        <v>199</v>
-      </c>
-      <c r="B99" s="176"/>
-      <c r="C99" s="176"/>
-      <c r="D99" s="176"/>
-      <c r="E99" s="176"/>
-      <c r="F99" s="176"/>
-      <c r="G99" s="177"/>
+      <c r="A99" s="181" t="s">
+        <v>200</v>
+      </c>
+      <c r="B99" s="182"/>
+      <c r="C99" s="182"/>
+      <c r="D99" s="182"/>
+      <c r="E99" s="182"/>
+      <c r="F99" s="182"/>
+      <c r="G99" s="183"/>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="39" t="s">
@@ -6671,16 +6779,16 @@
         <v>68</v>
       </c>
       <c r="C100" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D100" s="40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E100" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F100" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G100" s="40"/>
     </row>
@@ -6692,16 +6800,16 @@
         <v>71</v>
       </c>
       <c r="C101" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D101" s="40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F101" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G101" s="40"/>
     </row>
@@ -6713,16 +6821,16 @@
         <v>73</v>
       </c>
       <c r="C102" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D102" s="40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E102" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F102" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G102" s="40"/>
     </row>
@@ -6734,16 +6842,16 @@
         <v>75</v>
       </c>
       <c r="C103" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D103" s="40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F103" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G103" s="40"/>
     </row>
@@ -6755,19 +6863,19 @@
         <v>77</v>
       </c>
       <c r="C104" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D104" s="40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E104" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F104" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G104" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6778,19 +6886,19 @@
         <v>79</v>
       </c>
       <c r="C105" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D105" s="40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E105" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F105" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G105" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6801,19 +6909,19 @@
         <v>81</v>
       </c>
       <c r="C106" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D106" s="40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E106" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F106" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G106" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6824,19 +6932,19 @@
         <v>83</v>
       </c>
       <c r="C107" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D107" s="40" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E107" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F107" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G107" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6847,19 +6955,19 @@
         <v>85</v>
       </c>
       <c r="C108" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D108" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E108" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F108" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G108" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6870,19 +6978,19 @@
         <v>87</v>
       </c>
       <c r="C109" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D109" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E109" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F109" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G109" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6893,19 +7001,19 @@
         <v>89</v>
       </c>
       <c r="C110" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D110" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E110" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F110" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G110" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -6916,19 +7024,19 @@
         <v>93</v>
       </c>
       <c r="C111" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D111" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E111" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F111" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G111" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6939,19 +7047,19 @@
         <v>99</v>
       </c>
       <c r="C112" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D112" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E112" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F112" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G112" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6962,19 +7070,19 @@
         <v>101</v>
       </c>
       <c r="C113" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D113" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E113" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F113" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G113" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6985,19 +7093,19 @@
         <v>103</v>
       </c>
       <c r="C114" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D114" s="41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E114" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F114" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G114" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="29.25">
@@ -7008,19 +7116,19 @@
         <v>105</v>
       </c>
       <c r="C115" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D115" s="41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E115" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F115" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="E115" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F115" s="40" t="s">
-        <v>200</v>
-      </c>
       <c r="G115" s="40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="29.25">
@@ -7031,19 +7139,19 @@
         <v>107</v>
       </c>
       <c r="C116" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D116" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E116" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F116" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="G116" s="40" t="s">
         <v>203</v>
-      </c>
-      <c r="E116" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="F116" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="G116" s="40" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -7054,19 +7162,19 @@
         <v>113</v>
       </c>
       <c r="C117" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D117" s="41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E117" s="40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F117" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G117" s="40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -7077,19 +7185,19 @@
         <v>115</v>
       </c>
       <c r="C118" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D118" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E118" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F118" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G118" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -7100,19 +7208,19 @@
         <v>117</v>
       </c>
       <c r="C119" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D119" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E119" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F119" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G119" s="41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -7143,13 +7251,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34.5" customHeight="1">
-      <c r="A1" s="181" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
+      <c r="A1" s="187" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
     </row>
     <row r="2" spans="1:5" ht="27" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -7173,16 +7281,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D3" s="48" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="80.25" customHeight="1">
@@ -7190,16 +7298,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4" s="51" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="51" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7211,7 +7319,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="44"/>
@@ -7219,26 +7327,26 @@
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A7" s="181" t="s">
-        <v>211</v>
-      </c>
-      <c r="B7" s="182"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="182"/>
+      <c r="A7" s="187" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1">
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>66</v>
@@ -7249,16 +7357,16 @@
         <v>16</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E9" s="55" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7266,16 +7374,16 @@
         <v>16</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7283,16 +7391,16 @@
         <v>16</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E11" s="59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7300,16 +7408,16 @@
         <v>16</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D12" s="60">
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -7335,13 +7443,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1">
-      <c r="A1" s="181" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
+      <c r="A1" s="187" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
     </row>
     <row r="2" spans="1:5" ht="23.25" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -7365,7 +7473,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C3" s="62" t="s">
         <v>60</v>
@@ -7374,7 +7482,7 @@
         <v>56</v>
       </c>
       <c r="E3" s="62" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="249.75" customHeight="1">
@@ -7382,38 +7490,38 @@
         <v>2</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E4" s="64" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="44"/>
@@ -7421,26 +7529,26 @@
       <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="181" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="182"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="182"/>
-      <c r="E7" s="182"/>
+      <c r="A7" s="187" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>66</v>
@@ -7448,121 +7556,121 @@
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1">
       <c r="A9" s="66" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C9" s="54" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E9" s="67" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="93" customHeight="1">
       <c r="A10" s="68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E10" s="69" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="29.25">
       <c r="A11" s="68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E11" s="69" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="21" customHeight="1">
       <c r="A12" s="68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E12" s="69" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="24.75" customHeight="1">
       <c r="A13" s="68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E13" s="69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="52.5" customHeight="1">
       <c r="A14" s="68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E14" s="69" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="40.5" customHeight="1">
       <c r="A15" s="70" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D15" s="72" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E15" s="73" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -7592,14 +7700,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50.25" customHeight="1">
-      <c r="A1" s="181" t="s">
-        <v>251</v>
-      </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
+      <c r="A1" s="187" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="188"/>
     </row>
     <row r="2" spans="1:6" s="21" customFormat="1" ht="23.25" customHeight="1">
       <c r="A2" s="19" t="s">
@@ -7615,7 +7723,7 @@
         <v>51</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F2" s="20" t="s">
         <v>122</v>
@@ -7626,17 +7734,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="25"/>
       <c r="F3" s="25" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1">
@@ -7656,51 +7764,51 @@
       <c r="F5" s="25"/>
     </row>
     <row r="6" spans="1:6" ht="18.600000000000001" customHeight="1">
-      <c r="A6" s="183" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
+      <c r="A6" s="189" t="s">
+        <v>257</v>
+      </c>
+      <c r="B6" s="190"/>
+      <c r="C6" s="190"/>
+      <c r="D6" s="190"/>
+      <c r="E6" s="190"/>
+      <c r="F6" s="190"/>
     </row>
     <row r="7" spans="1:6" ht="19.5" customHeight="1">
       <c r="A7" s="81" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C7" s="82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D7" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="185" t="s">
+      <c r="E7" s="191" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="186"/>
+      <c r="F7" s="192"/>
     </row>
     <row r="8" spans="1:6" s="34" customFormat="1" ht="36" customHeight="1">
       <c r="A8" s="31" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D8" s="33" t="s">
         <v>90</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="34" customFormat="1" ht="36" customHeight="1">
@@ -7708,19 +7816,19 @@
         <v>14</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D9" s="33" t="s">
         <v>90</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="34" customFormat="1" ht="36" customHeight="1">
@@ -7731,13 +7839,13 @@
         <v>93</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D10" s="33" t="s">
         <v>69</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F10" s="35"/>
     </row>
@@ -7766,13 +7874,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A1" s="187" t="s">
-        <v>269</v>
-      </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="189"/>
+      <c r="A1" s="193" t="s">
+        <v>270</v>
+      </c>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="195"/>
       <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="19.5" customHeight="1">
@@ -7780,13 +7888,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>66</v>
@@ -7798,16 +7906,16 @@
         <v>29</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F3" s="9"/>
     </row>
@@ -7816,16 +7924,16 @@
         <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F4" s="9"/>
     </row>
@@ -7837,7 +7945,7 @@
         <v>79</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>69</v>
@@ -7855,7 +7963,7 @@
         <v>85</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>69</v>
@@ -7873,7 +7981,7 @@
         <v>87</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>69</v>
@@ -7891,7 +7999,7 @@
         <v>89</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>69</v>
@@ -7909,7 +8017,7 @@
         <v>93</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>69</v>
@@ -7927,7 +8035,7 @@
         <v>99</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>69</v>
@@ -7945,7 +8053,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>69</v>
@@ -7960,16 +8068,16 @@
         <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>275</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>274</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -7981,7 +8089,7 @@
         <v>77</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>69</v>
@@ -7996,16 +8104,16 @@
         <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F14" s="9"/>
     </row>
@@ -8014,16 +8122,16 @@
         <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F15" s="9"/>
     </row>
@@ -8035,7 +8143,7 @@
         <v>83</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>69</v>
@@ -8053,7 +8161,7 @@
         <v>81</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>69</v>
@@ -8068,16 +8176,16 @@
         <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F18" s="9"/>
     </row>
@@ -8086,16 +8194,16 @@
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F19" s="9"/>
     </row>
@@ -8104,16 +8212,16 @@
         <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D20" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F20" s="9"/>
     </row>
@@ -8125,7 +8233,7 @@
         <v>117</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>69</v>
@@ -8134,7 +8242,7 @@
         <v>117</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -8145,7 +8253,7 @@
         <v>71</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>69</v>
@@ -8177,13 +8285,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="29.25" customHeight="1">
-      <c r="A1" s="187" t="s">
-        <v>283</v>
-      </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="189"/>
+      <c r="A1" s="193" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="195"/>
       <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="19.5" customHeight="1">
@@ -8191,13 +8299,13 @@
         <v>32</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>66</v>
@@ -8209,16 +8317,16 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F3" s="9"/>
     </row>
@@ -8227,16 +8335,16 @@
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D4" s="17" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F4" s="9"/>
     </row>
@@ -8249,6 +8357,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8257,7 +8375,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -8429,24 +8547,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF058429-F5B4-4A8F-AEDD-B64B134BEA2E}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{921EC880-CEE1-4864-A95E-E1BCA8FFCF0E}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CC24F18-6B81-4826-B056-559BAD924699}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF058429-F5B4-4A8F-AEDD-B64B134BEA2E}"/>
 </file>